--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133573159</v>
+        <v>133573156</v>
       </c>
       <c r="B2" t="n">
         <v>79333</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635094</v>
+        <v>635142</v>
       </c>
       <c r="R2" t="n">
-        <v>6999463</v>
+        <v>6999378</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573156</v>
+        <v>133573159</v>
       </c>
       <c r="B3" t="n">
         <v>79333</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635142</v>
+        <v>635094</v>
       </c>
       <c r="R3" t="n">
-        <v>6999378</v>
+        <v>6999463</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,42 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R6" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R7" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1160,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R6" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,42 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R7" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,42 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R6" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R7" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573156</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>133573159</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>133573153</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1160,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R6" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,42 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R7" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1374,7 @@
         <v>133573155</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133573154</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>133566428</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>133566430</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,42 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R6" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R7" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1160,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R6" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,42 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R7" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>133573153</v>
       </c>
       <c r="B4" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,42 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R6" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R7" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573156</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>133573159</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>133573153</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>133573157</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1160,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R6" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,42 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R7" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1374,7 @@
         <v>133573155</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>133566423</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133573154</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>133566426</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>133566428</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>133566430</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133573156</v>
+        <v>133573159</v>
       </c>
       <c r="B2" t="n">
         <v>79348</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635142</v>
+        <v>635094</v>
       </c>
       <c r="R2" t="n">
-        <v>6999378</v>
+        <v>6999463</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573159</v>
+        <v>133573156</v>
       </c>
       <c r="B3" t="n">
         <v>79348</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635094</v>
+        <v>635142</v>
       </c>
       <c r="R3" t="n">
-        <v>6999463</v>
+        <v>6999378</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133573159</v>
+        <v>133573156</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635094</v>
+        <v>635142</v>
       </c>
       <c r="R2" t="n">
-        <v>6999463</v>
+        <v>6999378</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573156</v>
+        <v>133573159</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635142</v>
+        <v>635094</v>
       </c>
       <c r="R3" t="n">
-        <v>6999378</v>
+        <v>6999463</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +930,7 @@
         <v>133573153</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>133573157</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>133573155</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>133566423</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133573154</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>133566426</v>
       </c>
       <c r="B11" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>133566428</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>133566430</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133573156</v>
+        <v>133573159</v>
       </c>
       <c r="B2" t="n">
         <v>79358</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635142</v>
+        <v>635094</v>
       </c>
       <c r="R2" t="n">
-        <v>6999378</v>
+        <v>6999463</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573159</v>
+        <v>133573156</v>
       </c>
       <c r="B3" t="n">
         <v>79358</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635094</v>
+        <v>635142</v>
       </c>
       <c r="R3" t="n">
-        <v>6999463</v>
+        <v>6999378</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,42 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R6" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1267,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R7" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133573159</v>
+        <v>133573156</v>
       </c>
       <c r="B2" t="n">
         <v>79358</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635094</v>
+        <v>635142</v>
       </c>
       <c r="R2" t="n">
-        <v>6999463</v>
+        <v>6999378</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573156</v>
+        <v>133573159</v>
       </c>
       <c r="B3" t="n">
         <v>79358</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635142</v>
+        <v>635094</v>
       </c>
       <c r="R3" t="n">
-        <v>6999378</v>
+        <v>6999463</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133566421</v>
+        <v>133566424</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,34 +1160,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635301</v>
+        <v>635270</v>
       </c>
       <c r="R6" t="n">
-        <v>6999384</v>
+        <v>6999349</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133566424</v>
+        <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,42 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635270</v>
+        <v>635301</v>
       </c>
       <c r="R7" t="n">
-        <v>6999349</v>
+        <v>6999384</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573156</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>133573159</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>133573153</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>133566421</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>133573155</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>133573154</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>133566428</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>133566430</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 4524-2026 artfynd.xlsx
+++ b/artfynd/A 4524-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566431</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566433</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566435</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573151</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1768,6 +1813,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573154</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1894,6 +1944,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573155</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2020,6 +2075,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573156</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2146,6 +2206,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573159</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2261,6 +2326,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566423</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2376,6 +2446,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566424</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2491,6 +2566,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133566426</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2606,8 +2686,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133573157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>